--- a/start.xlsx
+++ b/start.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\YandexDisk\Python\Work\autoru_parser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{740F4E53-A124-4723-9979-B62D13F0C6F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{785593CD-5426-4A2D-BB14-12A8821CFAF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19200" yWindow="0" windowWidth="19200" windowHeight="15600" tabRatio="524" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38400" yWindow="0" windowWidth="19200" windowHeight="15600" tabRatio="524" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="По марке (автоматом)" sheetId="1" r:id="rId1"/>
@@ -20,9 +20,9 @@
     <sheet name="Инструкция" sheetId="3" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'По марке (автоматом)'!$A$1:$H$106</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'По марке (автоматом)'!$A$1:$H$107</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'По марке (автоматом)2'!$A$1:$H$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'По марке (по запросу)'!$A$1:$H$288</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'По марке (по запросу)'!$A$1:$H$289</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2751" uniqueCount="606">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2768" uniqueCount="611">
   <si>
     <t>Наш клиент</t>
   </si>
@@ -1868,6 +1868,21 @@
   </si>
   <si>
     <t>JLR ТЦ Кунцево</t>
+  </si>
+  <si>
+    <t>HiPhi (Москва)</t>
+  </si>
+  <si>
+    <t>Авилон Электро</t>
+  </si>
+  <si>
+    <t>https://cabinet.auto.ru/sales/cars/new/</t>
+  </si>
+  <si>
+    <t>avilon.electro@rambler.ru</t>
+  </si>
+  <si>
+    <t>4w5whDSaaDER</t>
   </si>
 </sst>
 </file>
@@ -2329,7 +2344,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Лист1"/>
-  <dimension ref="A1:K108"/>
+  <dimension ref="A1:K109"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="31.140625" style="7" customWidth="1"/>
@@ -3107,19 +3122,19 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>256</v>
+        <v>606</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="D32" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="F32" s="7" t="s">
         <v>12</v>
@@ -3130,19 +3145,19 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>201</v>
+        <v>72</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>201</v>
+        <v>72</v>
       </c>
       <c r="D33" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>224</v>
+        <v>71</v>
       </c>
       <c r="F33" s="7" t="s">
         <v>12</v>
@@ -3153,19 +3168,19 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D34" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F34" s="7" t="s">
         <v>12</v>
@@ -3176,19 +3191,19 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D35" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F35" s="7" t="s">
         <v>12</v>
@@ -3199,19 +3214,19 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>27</v>
+        <v>203</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>27</v>
+        <v>203</v>
       </c>
       <c r="D36" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>28</v>
+        <v>226</v>
       </c>
       <c r="F36" s="7" t="s">
         <v>12</v>
@@ -3222,19 +3237,19 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>181</v>
+        <v>27</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>181</v>
+        <v>27</v>
       </c>
       <c r="D37" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>182</v>
+        <v>28</v>
       </c>
       <c r="F37" s="7" t="s">
         <v>12</v>
@@ -3245,19 +3260,19 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>157</v>
+        <v>181</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>157</v>
+        <v>181</v>
       </c>
       <c r="D38" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>158</v>
+        <v>182</v>
       </c>
       <c r="F38" s="7" t="s">
         <v>12</v>
@@ -3268,19 +3283,19 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>204</v>
+        <v>157</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>204</v>
+        <v>157</v>
       </c>
       <c r="D39" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>227</v>
+        <v>158</v>
       </c>
       <c r="F39" s="7" t="s">
         <v>12</v>
@@ -3291,19 +3306,19 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D40" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F40" s="7" t="s">
         <v>12</v>
@@ -3314,19 +3329,19 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="D41" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E41" t="s">
-        <v>239</v>
+      <c r="E41" s="7" t="s">
+        <v>228</v>
       </c>
       <c r="F41" s="7" t="s">
         <v>12</v>
@@ -3337,19 +3352,19 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>37</v>
+        <v>189</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>37</v>
+        <v>189</v>
       </c>
       <c r="D42" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E42" s="7" t="s">
-        <v>38</v>
+      <c r="E42" t="s">
+        <v>239</v>
       </c>
       <c r="F42" s="7" t="s">
         <v>12</v>
@@ -3360,19 +3375,19 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>206</v>
+        <v>37</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>206</v>
+        <v>37</v>
       </c>
       <c r="D43" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>95</v>
+        <v>38</v>
       </c>
       <c r="F43" s="7" t="s">
         <v>12</v>
@@ -3383,19 +3398,19 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>78</v>
+        <v>206</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>78</v>
+        <v>206</v>
       </c>
       <c r="D44" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="F44" s="7" t="s">
         <v>12</v>
@@ -3406,19 +3421,19 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>21</v>
+        <v>78</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>21</v>
+        <v>78</v>
       </c>
       <c r="D45" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="F45" s="7" t="s">
         <v>12</v>
@@ -3429,19 +3444,19 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="D46" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="F46" s="7" t="s">
         <v>12</v>
@@ -3452,19 +3467,19 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="D47" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>229</v>
+        <v>82</v>
       </c>
       <c r="F47" s="7" t="s">
         <v>12</v>
@@ -3475,19 +3490,19 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>207</v>
+        <v>98</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>207</v>
+        <v>98</v>
       </c>
       <c r="D48" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F48" s="7" t="s">
         <v>12</v>
@@ -3498,19 +3513,19 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>24</v>
+        <v>207</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>24</v>
+        <v>207</v>
       </c>
       <c r="D49" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>25</v>
+        <v>230</v>
       </c>
       <c r="F49" s="7" t="s">
         <v>12</v>
@@ -3521,19 +3536,19 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>208</v>
+        <v>24</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>208</v>
+        <v>24</v>
       </c>
       <c r="D50" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>231</v>
+        <v>25</v>
       </c>
       <c r="F50" s="7" t="s">
         <v>12</v>
@@ -3544,19 +3559,19 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D51" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F51" s="7" t="s">
         <v>12</v>
@@ -3567,19 +3582,19 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>159</v>
+        <v>209</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>159</v>
+        <v>209</v>
       </c>
       <c r="D52" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>160</v>
+        <v>232</v>
       </c>
       <c r="F52" s="7" t="s">
         <v>12</v>
@@ -3590,19 +3605,19 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>210</v>
+        <v>159</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>210</v>
+        <v>159</v>
       </c>
       <c r="D53" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>233</v>
+        <v>160</v>
       </c>
       <c r="F53" s="7" t="s">
         <v>12</v>
@@ -3613,19 +3628,19 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D54" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F54" s="7" t="s">
         <v>12</v>
@@ -3636,19 +3651,19 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>124</v>
+        <v>211</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>124</v>
+        <v>211</v>
       </c>
       <c r="D55" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F55" s="7" t="s">
         <v>12</v>
@@ -3659,19 +3674,19 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D56" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F56" s="7" t="s">
         <v>12</v>
@@ -3682,19 +3697,19 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>212</v>
+        <v>125</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>212</v>
+        <v>125</v>
       </c>
       <c r="D57" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F57" s="7" t="s">
         <v>12</v>
@@ -3705,19 +3720,19 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D58" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F58" s="7" t="s">
         <v>12</v>
@@ -3728,19 +3743,19 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>100</v>
+        <v>213</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>100</v>
+        <v>213</v>
       </c>
       <c r="D59" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>99</v>
+        <v>238</v>
       </c>
       <c r="F59" s="7" t="s">
         <v>12</v>
@@ -3751,19 +3766,19 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>154</v>
+        <v>100</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>154</v>
+        <v>100</v>
       </c>
       <c r="D60" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E60" t="s">
-        <v>153</v>
+      <c r="E60" s="7" t="s">
+        <v>99</v>
       </c>
       <c r="F60" s="7" t="s">
         <v>12</v>
@@ -3774,19 +3789,19 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>240</v>
+        <v>154</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>240</v>
+        <v>154</v>
       </c>
       <c r="D61" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E61" t="s">
-        <v>241</v>
+        <v>153</v>
       </c>
       <c r="F61" s="7" t="s">
         <v>12</v>
@@ -3797,22 +3812,22 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>31</v>
+        <v>240</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>31</v>
+        <v>240</v>
       </c>
       <c r="D62" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E62" s="7" t="s">
-        <v>109</v>
+      <c r="E62" t="s">
+        <v>241</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G62" s="7" t="s">
         <v>18</v>
@@ -3820,19 +3835,19 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>192</v>
+        <v>31</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>192</v>
+        <v>31</v>
       </c>
       <c r="D63" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>330</v>
+        <v>109</v>
       </c>
       <c r="F63" s="7" t="s">
         <v>17</v>
@@ -3843,19 +3858,19 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="7" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>34</v>
+        <v>192</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>34</v>
+        <v>192</v>
       </c>
       <c r="D64" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E64" s="7" t="s">
-        <v>138</v>
+        <v>330</v>
       </c>
       <c r="F64" s="7" t="s">
         <v>17</v>
@@ -3866,19 +3881,19 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>91</v>
+        <v>34</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>91</v>
+        <v>34</v>
       </c>
       <c r="D65" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>331</v>
+        <v>138</v>
       </c>
       <c r="F65" s="7" t="s">
         <v>17</v>
@@ -3889,19 +3904,19 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>193</v>
+        <v>91</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>193</v>
+        <v>91</v>
       </c>
       <c r="D66" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E66" s="7" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F66" s="7" t="s">
         <v>17</v>
@@ -3912,19 +3927,19 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D67" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E67" s="7" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F67" s="7" t="s">
         <v>17</v>
@@ -3935,19 +3950,19 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="7" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>67</v>
+        <v>194</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>67</v>
+        <v>194</v>
       </c>
       <c r="D68" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E68" s="7" t="s">
-        <v>110</v>
+        <v>333</v>
       </c>
       <c r="F68" s="7" t="s">
         <v>17</v>
@@ -3958,19 +3973,19 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>195</v>
+        <v>67</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>195</v>
+        <v>67</v>
       </c>
       <c r="D69" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E69" s="7" t="s">
-        <v>334</v>
+        <v>110</v>
       </c>
       <c r="F69" s="7" t="s">
         <v>17</v>
@@ -3981,19 +3996,19 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="7" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D70" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E70" s="7" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F70" s="7" t="s">
         <v>17</v>
@@ -4004,19 +4019,19 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D71" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F71" s="7" t="s">
         <v>17</v>
@@ -4027,19 +4042,19 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="7" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D72" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E72" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F72" s="7" t="s">
         <v>17</v>
@@ -4050,19 +4065,19 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>43</v>
+        <v>198</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>43</v>
+        <v>198</v>
       </c>
       <c r="D73" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E73" s="7" t="s">
-        <v>185</v>
+        <v>337</v>
       </c>
       <c r="F73" s="7" t="s">
         <v>17</v>
@@ -4073,19 +4088,19 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="7" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>199</v>
+        <v>43</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>199</v>
+        <v>43</v>
       </c>
       <c r="D74" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E74" s="7" t="s">
-        <v>338</v>
+        <v>185</v>
       </c>
       <c r="F74" s="7" t="s">
         <v>17</v>
@@ -4096,19 +4111,19 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D75" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E75" s="7" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F75" s="7" t="s">
         <v>17</v>
@@ -4119,19 +4134,19 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="7" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>72</v>
+        <v>200</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>72</v>
+        <v>200</v>
       </c>
       <c r="D76" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E76" s="7" t="s">
-        <v>139</v>
+        <v>339</v>
       </c>
       <c r="F76" s="7" t="s">
         <v>17</v>
@@ -4142,19 +4157,19 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>201</v>
+        <v>72</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>201</v>
+        <v>72</v>
       </c>
       <c r="D77" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E77" s="7" t="s">
-        <v>340</v>
+        <v>139</v>
       </c>
       <c r="F77" s="7" t="s">
         <v>17</v>
@@ -4165,19 +4180,19 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="7" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D78" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E78" s="7" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F78" s="7" t="s">
         <v>17</v>
@@ -4188,19 +4203,19 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D79" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E79" s="7" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F79" s="7" t="s">
         <v>17</v>
@@ -4211,19 +4226,19 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="7" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>27</v>
+        <v>203</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>27</v>
+        <v>203</v>
       </c>
       <c r="D80" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E80" s="7" t="s">
-        <v>140</v>
+        <v>342</v>
       </c>
       <c r="F80" s="7" t="s">
         <v>17</v>
@@ -4234,19 +4249,19 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>181</v>
+        <v>27</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>181</v>
+        <v>27</v>
       </c>
       <c r="D81" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E81" s="7" t="s">
-        <v>343</v>
+        <v>140</v>
       </c>
       <c r="F81" s="7" t="s">
         <v>17</v>
@@ -4257,19 +4272,19 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>157</v>
+        <v>181</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>157</v>
+        <v>181</v>
       </c>
       <c r="D82" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E82" s="7" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F82" s="7" t="s">
         <v>17</v>
@@ -4280,19 +4295,19 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>204</v>
+        <v>157</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>204</v>
+        <v>157</v>
       </c>
       <c r="D83" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E83" s="7" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F83" s="7" t="s">
         <v>17</v>
@@ -4303,19 +4318,19 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="7" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D84" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E84" s="7" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F84" s="7" t="s">
         <v>17</v>
@@ -4326,19 +4341,19 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="D85" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E85" t="s">
-        <v>188</v>
+      <c r="E85" s="7" t="s">
+        <v>346</v>
       </c>
       <c r="F85" s="7" t="s">
         <v>17</v>
@@ -4349,19 +4364,19 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="7" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>37</v>
+        <v>189</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>37</v>
+        <v>189</v>
       </c>
       <c r="D86" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E86" s="7" t="s">
-        <v>141</v>
+      <c r="E86" t="s">
+        <v>188</v>
       </c>
       <c r="F86" s="7" t="s">
         <v>17</v>
@@ -4372,19 +4387,19 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>206</v>
+        <v>37</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>206</v>
+        <v>37</v>
       </c>
       <c r="D87" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E87" s="7" t="s">
-        <v>347</v>
+        <v>141</v>
       </c>
       <c r="F87" s="7" t="s">
         <v>17</v>
@@ -4395,19 +4410,19 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="7" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>78</v>
+        <v>206</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>78</v>
+        <v>206</v>
       </c>
       <c r="D88" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E88" s="7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F88" s="7" t="s">
         <v>17</v>
@@ -4418,19 +4433,19 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>21</v>
+        <v>78</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>21</v>
+        <v>78</v>
       </c>
       <c r="D89" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E89" s="7" t="s">
-        <v>137</v>
+        <v>348</v>
       </c>
       <c r="F89" s="7" t="s">
         <v>17</v>
@@ -4441,19 +4456,19 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="7" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B90" s="7" t="s">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="D90" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E90" s="7" t="s">
-        <v>349</v>
+        <v>137</v>
       </c>
       <c r="F90" s="7" t="s">
         <v>17</v>
@@ -4464,19 +4479,19 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="D91" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E91" s="7" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F91" s="7" t="s">
         <v>17</v>
@@ -4487,19 +4502,19 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="7" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B92" s="7" t="s">
-        <v>207</v>
+        <v>98</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>207</v>
+        <v>98</v>
       </c>
       <c r="D92" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E92" s="7" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F92" s="7" t="s">
         <v>17</v>
@@ -4510,19 +4525,19 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B93" s="7" t="s">
-        <v>24</v>
+        <v>207</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>24</v>
+        <v>207</v>
       </c>
       <c r="D93" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E93" s="7" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F93" s="7" t="s">
         <v>17</v>
@@ -4533,19 +4548,19 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="7" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B94" s="7" t="s">
-        <v>208</v>
+        <v>24</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>208</v>
+        <v>24</v>
       </c>
       <c r="D94" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E94" s="7" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F94" s="7" t="s">
         <v>17</v>
@@ -4556,19 +4571,19 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B95" s="7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D95" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E95" s="7" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F95" s="7" t="s">
         <v>17</v>
@@ -4579,19 +4594,19 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="7" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B96" s="7" t="s">
-        <v>159</v>
+        <v>209</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>159</v>
+        <v>209</v>
       </c>
       <c r="D96" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E96" s="7" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F96" s="7" t="s">
         <v>17</v>
@@ -4602,19 +4617,19 @@
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B97" s="7" t="s">
-        <v>210</v>
+        <v>159</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>210</v>
+        <v>159</v>
       </c>
       <c r="D97" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E97" s="7" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="F97" s="7" t="s">
         <v>17</v>
@@ -4625,19 +4640,19 @@
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" s="7" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B98" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D98" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E98" s="7" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F98" s="7" t="s">
         <v>17</v>
@@ -4648,19 +4663,19 @@
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B99" s="7" t="s">
-        <v>124</v>
+        <v>211</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>124</v>
+        <v>211</v>
       </c>
       <c r="D99" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E99" s="7" t="s">
-        <v>142</v>
+        <v>358</v>
       </c>
       <c r="F99" s="7" t="s">
         <v>17</v>
@@ -4671,19 +4686,19 @@
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" s="7" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B100" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D100" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E100" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F100" s="7" t="s">
         <v>17</v>
@@ -4694,19 +4709,19 @@
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B101" s="7" t="s">
-        <v>212</v>
+        <v>125</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>212</v>
+        <v>125</v>
       </c>
       <c r="D101" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E101" s="7" t="s">
-        <v>359</v>
+        <v>143</v>
       </c>
       <c r="F101" s="7" t="s">
         <v>17</v>
@@ -4717,19 +4732,19 @@
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" s="7" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B102" s="7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D102" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E102" s="7" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F102" s="7" t="s">
         <v>17</v>
@@ -4740,19 +4755,19 @@
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B103" s="7" t="s">
-        <v>100</v>
+        <v>213</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>100</v>
+        <v>213</v>
       </c>
       <c r="D103" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E103" s="7" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F103" s="7" t="s">
         <v>17</v>
@@ -4763,19 +4778,19 @@
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" s="7" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B104" s="7" t="s">
-        <v>154</v>
+        <v>100</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>154</v>
+        <v>100</v>
       </c>
       <c r="D104" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E104" t="s">
-        <v>362</v>
+      <c r="E104" s="7" t="s">
+        <v>361</v>
       </c>
       <c r="F104" s="7" t="s">
         <v>17</v>
@@ -4786,19 +4801,19 @@
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="B105" s="7" t="s">
-        <v>240</v>
+        <v>154</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>240</v>
+        <v>154</v>
       </c>
       <c r="D105" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E105" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="F105" s="7" t="s">
         <v>17</v>
@@ -4809,32 +4824,55 @@
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="B106" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="C106" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="D106" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E106" t="s">
+        <v>356</v>
+      </c>
+      <c r="F106" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G106" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A107" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B106" s="7" t="s">
+      <c r="B107" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C106" s="7" t="s">
+      <c r="C107" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D106" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E106" s="7" t="s">
+      <c r="D107" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E107" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="F106" s="7" t="s">
+      <c r="F107" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="H106" s="7" t="s">
+      <c r="H107" s="7" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K108" s="9"/>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K109" s="9"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H106" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:H107" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A13:AMJ17">
     <sortCondition ref="A13:A17"/>
   </sortState>
@@ -5315,7 +5353,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Лист2"/>
-  <dimension ref="A1:AMJ288"/>
+  <dimension ref="A1:AMJ289"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="31.140625" style="1" customWidth="1"/>
@@ -7972,9 +8010,6 @@
       <c r="F78" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G78" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="H78"/>
     </row>
     <row r="79" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11973,6 +12008,9 @@
       <c r="F264" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="G264" s="1" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="265" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
@@ -12455,8 +12493,29 @@
       </c>
       <c r="H288" s="5"/>
     </row>
+    <row r="289" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A289" s="7" t="s">
+        <v>606</v>
+      </c>
+      <c r="B289" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C289" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D289" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E289" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="F289" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G289" s="7"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H288" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
+  <autoFilter ref="A1:H289" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A214:AMJ222">
     <sortCondition ref="G214:G222"/>
     <sortCondition ref="A214:A222"/>
@@ -12509,7 +12568,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D02ACF4A-BD8C-4914-967C-7647CD809D86}">
   <sheetPr codeName="Лист5"/>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
@@ -12558,7 +12617,21 @@
       <c r="D4" t="s">
         <v>591</v>
       </c>
-      <c r="E4" t="s">
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>607</v>
+      </c>
+      <c r="B5" t="s">
+        <v>609</v>
+      </c>
+      <c r="C5" t="s">
+        <v>610</v>
+      </c>
+      <c r="D5" t="s">
+        <v>608</v>
+      </c>
+      <c r="E5" t="s">
         <v>18</v>
       </c>
     </row>
